--- a/data/trans_dic/P6905-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P6905-Clase-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene dolores de cabeza</t>
+          <t>Población que su trabajo le afecta de manera que tiene dolores de cabeza (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23,16; 47,29</t>
+          <t>22,95; 46,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21,07; 47,68</t>
+          <t>22,13; 48,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27,79; 57,92</t>
+          <t>27,28; 58,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,58; 50,88</t>
+          <t>22,35; 52,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,86; 53,04</t>
+          <t>24,41; 54,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,76; 59,99</t>
+          <t>31,43; 61,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,97; 46,78</t>
+          <t>17,11; 45,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32,23; 54,39</t>
+          <t>32,1; 54,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27,63; 44,65</t>
+          <t>26,42; 45,25</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29,36; 49,27</t>
+          <t>28,57; 48,69</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26,75; 48,18</t>
+          <t>26,03; 46,38</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30,98; 48,88</t>
+          <t>30,91; 47,82</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,6; 42,59</t>
+          <t>13,31; 42,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,94; 47,79</t>
+          <t>17,03; 47,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,91; 54,32</t>
+          <t>18,31; 54,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,09; 39,98</t>
+          <t>13,49; 38,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>54,2; 81,76</t>
+          <t>52,82; 81,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,29; 81,45</t>
+          <t>40,05; 80,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,65; 60,93</t>
+          <t>23,08; 58,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,64; 48,82</t>
+          <t>24,15; 50,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37,06; 58,95</t>
+          <t>37,19; 58,59</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30,37; 58,28</t>
+          <t>31,22; 57,53</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24,91; 50,52</t>
+          <t>26,12; 51,4</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,32; 40,81</t>
+          <t>21,68; 40,32</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31,71; 51,6</t>
+          <t>31,97; 52,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,84; 35,45</t>
+          <t>15,32; 34,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,86; 32,96</t>
+          <t>12,19; 32,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,43; 36,03</t>
+          <t>12,25; 38,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,53; 69,3</t>
+          <t>20,2; 69,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,11; 55,6</t>
+          <t>21,61; 58,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,27; 90,14</t>
+          <t>22,55; 88,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,55; 50,85</t>
+          <t>15,45; 52,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32,16; 51,91</t>
+          <t>31,92; 50,86</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20,71; 38,18</t>
+          <t>19,99; 37,73</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17,38; 36,4</t>
+          <t>17,48; 36,8</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,36; 35,56</t>
+          <t>15,3; 35,53</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,51; 34,24</t>
+          <t>20,84; 34,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,52; 30,06</t>
+          <t>14,02; 29,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,22; 31,52</t>
+          <t>16,36; 31,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,43; 28,45</t>
+          <t>11,46; 30,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>34,03; 61,86</t>
+          <t>32,69; 61,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,31; 44,15</t>
+          <t>21,48; 44,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,8; 56,62</t>
+          <t>33,99; 56,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24,26; 40,51</t>
+          <t>24,61; 39,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,74; 38,09</t>
+          <t>25,72; 37,67</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,0; 31,89</t>
+          <t>18,74; 32,51</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24,58; 37,86</t>
+          <t>25,38; 38,29</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,4; 31,42</t>
+          <t>19,83; 30,97</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,14; 32,56</t>
+          <t>10,9; 31,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,14; 45,46</t>
+          <t>15,72; 45,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,09; 39,97</t>
+          <t>18,01; 40,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,57; 32,02</t>
+          <t>9,24; 32,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,59; 32,21</t>
+          <t>12,0; 31,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,08; 53,93</t>
+          <t>23,95; 53,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,71; 57,0</t>
+          <t>30,41; 57,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,87; 39,66</t>
+          <t>12,29; 40,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,11; 28,33</t>
+          <t>13,93; 28,66</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23,53; 45,53</t>
+          <t>23,95; 45,36</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24,96; 43,01</t>
+          <t>25,14; 43,67</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,55; 34,14</t>
+          <t>13,06; 33,99</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1349,62 +1349,62 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,67%</t>
         </is>
       </c>
     </row>
@@ -1417,221 +1417,80 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>26,21; 35,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>21,42; 30,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>22,48; 32,17</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>18,32; 28,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>34,53; 47,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>33,72; 48,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>34,46; 48,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>23,33; 37,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>29,6; 37,08</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>28,28; 35,76</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>28,62; 36,76</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>22,68; 31,42</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>30,04%</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>25,99%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>27,16%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>22,84%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>40,96%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>40,98%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>41,41%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>32,32%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>33,51%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>31,95%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>32,6%</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>27,67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>25,47; 34,65</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>21,41; 31,37</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>22,91; 32,71</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>17,89; 29,25</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>35,05; 47,36</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>34,47; 48,33</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>34,99; 48,37</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>23,5; 37,83</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>30,19; 37,43</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>27,81; 36,27</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>28,26; 36,42</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>23,28; 31,64</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
@@ -1647,7 +1506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1669,7 +1528,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene dolores de cabeza</t>
+          <t>Población que su trabajo le afecta de manera que tiene dolores de cabeza (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1786,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>15073; 30781</t>
+          <t>14938; 30544</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11686; 26444</t>
+          <t>12271; 26764</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13038; 27172</t>
+          <t>12795; 27373</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10347; 23311</t>
+          <t>10241; 23877</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11131; 24744</t>
+          <t>11385; 25294</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13494; 26318</t>
+          <t>13788; 26887</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8253; 21490</t>
+          <t>7861; 20905</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19109; 32246</t>
+          <t>19030; 32572</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>30867; 49892</t>
+          <t>29519; 50557</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29160; 48937</t>
+          <t>28376; 48361</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24837; 44731</t>
+          <t>24169; 43063</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>32566; 51376</t>
+          <t>32491; 50258</t>
         </is>
       </c>
     </row>
@@ -2135,62 +1994,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6185; 18040</t>
+          <t>5639; 17930</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5794; 17368</t>
+          <t>6190; 17366</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5717; 16423</t>
+          <t>5537; 16468</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7157; 20300</t>
+          <t>6850; 19711</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22555; 34024</t>
+          <t>21983; 34024</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10723; 21678</t>
+          <t>10659; 21403</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6953; 17909</t>
+          <t>6784; 17142</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9543; 20580</t>
+          <t>10180; 21200</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31117; 49498</t>
+          <t>31227; 49201</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19120; 36691</t>
+          <t>19654; 36217</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14855; 30126</t>
+          <t>15576; 30650</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19814; 37926</t>
+          <t>20148; 37470</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2202,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31723; 51614</t>
+          <t>31980; 52409</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11626; 27771</t>
+          <t>12000; 27355</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8603; 22045</t>
+          <t>8155; 22040</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6688; 21087</t>
+          <t>7168; 22259</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2367; 11287</t>
+          <t>3289; 11255</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7455; 18749</t>
+          <t>7288; 19648</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2323; 8625</t>
+          <t>2158; 8511</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2774; 9072</t>
+          <t>2755; 9297</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>37408; 60374</t>
+          <t>37132; 59153</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23205; 42789</t>
+          <t>22407; 42278</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13289; 27832</t>
+          <t>13367; 28136</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11731; 27154</t>
+          <t>11682; 27128</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2410,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41196; 68769</t>
+          <t>41861; 70268</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16726; 34631</t>
+          <t>16154; 34238</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22197; 43136</t>
+          <t>22389; 43391</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15224; 37894</t>
+          <t>15264; 40003</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16996; 30896</t>
+          <t>16327; 30959</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13598; 29564</t>
+          <t>14383; 30033</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29261; 47607</t>
+          <t>28576; 47216</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25653; 42846</t>
+          <t>26026; 42273</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>64540; 95514</t>
+          <t>64510; 94477</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>34612; 58086</t>
+          <t>34134; 59226</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>54312; 83652</t>
+          <t>56083; 84598</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>46354; 75087</t>
+          <t>47396; 74000</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2618,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7131; 20840</t>
+          <t>6977; 20291</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6455; 18184</t>
+          <t>6289; 18192</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11807; 27614</t>
+          <t>12443; 27653</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4898; 16385</t>
+          <t>4728; 16555</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7606; 21137</t>
+          <t>7874; 20826</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10516; 23552</t>
+          <t>10459; 23143</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13588; 26973</t>
+          <t>14393; 27382</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>13836; 50472</t>
+          <t>15636; 51841</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>18292; 36720</t>
+          <t>18053; 37149</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19692; 38092</t>
+          <t>20036; 37954</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29062; 50067</t>
+          <t>29263; 50844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>22387; 60919</t>
+          <t>23304; 60637</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2831,62 +2690,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>131</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>87</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>150</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>219</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>161</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>224</t>
         </is>
       </c>
     </row>
@@ -2899,62 +2758,62 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>141892</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>84545</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>95064</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>77549</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>90168</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>88049</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>89574</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>113876</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>232061</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>172594</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>184638</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>191425</t>
         </is>
       </c>
     </row>
@@ -2967,282 +2826,74 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>123771; 166150</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>69688; 100601</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>78681; 112585</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>62196; 97889</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>76002; 104901</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>72440; 103677</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>74529; 104549</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>82181; 133524</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>204964; 256786</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>152744; 193169</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>162076; 208156</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>156898; 217349</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>141892</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>84545</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>95064</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>77549</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>90168</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>88049</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>89574</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>113876</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>232061</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>172594</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>184638</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>191425</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>120280; 163652</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>69651; 102071</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>80193; 114490</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>60738; 99292</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>77154; 104241</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>74043; 103828</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>75682; 104613</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>82775; 133288</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>209046; 259159</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>150211; 195919</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>160012; 206249</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>161060; 218917</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
@@ -3252,7 +2903,6 @@
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="K1:N1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_dic/P6905-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P6905-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>41,61%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>22,95; 46,93</t>
+          <t>22,71; 46,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,13; 48,26</t>
+          <t>22,32; 49,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27,28; 58,35</t>
+          <t>26,7; 56,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,35; 52,12</t>
+          <t>27,06; 57,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,41; 54,22</t>
+          <t>24,41; 52,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,43; 61,29</t>
+          <t>30,17; 59,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,11; 45,51</t>
+          <t>18,58; 46,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32,1; 54,94</t>
+          <t>29,14; 52,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,42; 45,25</t>
+          <t>26,22; 43,99</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28,57; 48,69</t>
+          <t>29,84; 49,78</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26,03; 46,38</t>
+          <t>25,93; 46,35</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30,91; 47,82</t>
+          <t>33,13; 51,78</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>30,31%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,31; 42,33</t>
+          <t>14,44; 43,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,03; 47,78</t>
+          <t>17,11; 48,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,31; 54,46</t>
+          <t>18,45; 53,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,49; 38,82</t>
+          <t>13,44; 39,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>52,82; 81,76</t>
+          <t>54,02; 81,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,05; 80,42</t>
+          <t>40,09; 82,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,08; 58,32</t>
+          <t>23,28; 60,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>24,15; 50,29</t>
+          <t>24,78; 50,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37,19; 58,59</t>
+          <t>36,06; 58,33</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31,22; 57,53</t>
+          <t>30,2; 56,04</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26,12; 51,4</t>
+          <t>25,91; 52,36</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,68; 40,32</t>
+          <t>21,13; 40,08</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>26,52%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31,97; 52,39</t>
+          <t>32,06; 52,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,32; 34,92</t>
+          <t>14,55; 35,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,19; 32,95</t>
+          <t>13,37; 34,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,25; 38,03</t>
+          <t>13,69; 41,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,2; 69,1</t>
+          <t>20,52; 70,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,61; 58,26</t>
+          <t>21,62; 56,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,55; 88,94</t>
+          <t>22,48; 89,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,45; 52,12</t>
+          <t>16,76; 48,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31,92; 50,86</t>
+          <t>32,22; 51,08</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19,99; 37,73</t>
+          <t>20,49; 38,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17,48; 36,8</t>
+          <t>16,94; 37,74</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,3; 35,53</t>
+          <t>17,1; 39,45</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>26,87%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,84; 34,99</t>
+          <t>21,25; 33,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,02; 29,72</t>
+          <t>14,15; 30,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,36; 31,7</t>
+          <t>16,41; 31,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,46; 30,03</t>
+          <t>16,21; 33,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,69; 61,99</t>
+          <t>35,4; 62,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,48; 44,85</t>
+          <t>22,48; 45,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,99; 56,16</t>
+          <t>33,96; 57,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24,61; 39,97</t>
+          <t>24,36; 39,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,72; 37,67</t>
+          <t>24,95; 37,04</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,74; 32,51</t>
+          <t>19,27; 32,48</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25,38; 38,29</t>
+          <t>25,08; 38,03</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,83; 30,97</t>
+          <t>21,19; 32,84</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>25,04%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,9; 31,7</t>
+          <t>10,09; 31,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,72; 45,48</t>
+          <t>15,85; 45,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,01; 40,02</t>
+          <t>17,99; 40,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,24; 32,35</t>
+          <t>7,93; 27,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,0; 31,74</t>
+          <t>11,69; 31,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,95; 53,0</t>
+          <t>24,04; 56,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,41; 57,86</t>
+          <t>30,25; 58,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,29; 40,74</t>
+          <t>23,42; 39,67</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,93; 28,66</t>
+          <t>13,9; 27,97</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23,95; 45,36</t>
+          <t>24,11; 45,67</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25,14; 43,67</t>
+          <t>25,38; 43,03</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,06; 33,99</t>
+          <t>19,71; 32,59</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>29,18%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26,21; 35,18</t>
+          <t>25,66; 34,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21,42; 30,92</t>
+          <t>21,08; 31,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22,48; 32,17</t>
+          <t>22,77; 32,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18,32; 28,83</t>
+          <t>20,28; 30,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>34,53; 47,66</t>
+          <t>34,12; 48,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33,72; 48,26</t>
+          <t>33,92; 47,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>34,46; 48,34</t>
+          <t>34,96; 48,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23,33; 37,9</t>
+          <t>29,27; 38,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29,6; 37,08</t>
+          <t>29,8; 37,02</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28,28; 35,76</t>
+          <t>28,2; 36,87</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28,62; 36,76</t>
+          <t>28,67; 36,51</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>22,68; 31,42</t>
+          <t>25,79; 33,38</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16057</t>
+          <t>22040</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>25327</t>
+          <t>25421</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>41384</t>
+          <t>47461</t>
         </is>
       </c>
     </row>
@@ -1786,62 +1786,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14938; 30544</t>
+          <t>14781; 30552</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12271; 26764</t>
+          <t>12380; 27185</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12795; 27373</t>
+          <t>12525; 26357</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10241; 23877</t>
+          <t>14080; 30004</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11385; 25294</t>
+          <t>11387; 24419</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13788; 26887</t>
+          <t>13237; 26018</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7861; 20905</t>
+          <t>8537; 21163</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19030; 32572</t>
+          <t>18073; 32368</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>29519; 50557</t>
+          <t>29293; 49154</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28376; 48361</t>
+          <t>29643; 49447</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24169; 43063</t>
+          <t>24071; 43035</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>32491; 50258</t>
+          <t>37794; 59068</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12689</t>
+          <t>12868</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15234</t>
+          <t>16685</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>27923</t>
+          <t>29553</t>
         </is>
       </c>
     </row>
@@ -1994,62 +1994,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5639; 17930</t>
+          <t>6115; 18226</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6190; 17366</t>
+          <t>6218; 17482</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5537; 16468</t>
+          <t>5580; 16169</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6850; 19711</t>
+          <t>6998; 20423</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21983; 34024</t>
+          <t>22479; 33868</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10659; 21403</t>
+          <t>10669; 22042</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6784; 17142</t>
+          <t>6843; 17919</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10180; 21200</t>
+          <t>11262; 22872</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31227; 49201</t>
+          <t>30278; 48984</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19654; 36217</t>
+          <t>19013; 35283</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15576; 30650</t>
+          <t>15452; 31224</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20148; 37470</t>
+          <t>20601; 39083</t>
         </is>
       </c>
     </row>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12866</t>
+          <t>15448</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5428</t>
+          <t>6287</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18295</t>
+          <t>21735</t>
         </is>
       </c>
     </row>
@@ -2202,62 +2202,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31980; 52409</t>
+          <t>32071; 52471</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12000; 27355</t>
+          <t>11397; 27560</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8155; 22040</t>
+          <t>8944; 22944</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7168; 22259</t>
+          <t>8416; 25529</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3289; 11255</t>
+          <t>3343; 11446</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7288; 19648</t>
+          <t>7292; 19197</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2158; 8511</t>
+          <t>2151; 8582</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2755; 9297</t>
+          <t>3429; 10004</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>37132; 59153</t>
+          <t>37472; 59417</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22407; 42278</t>
+          <t>22964; 43420</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13367; 28136</t>
+          <t>12953; 28855</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11682; 27128</t>
+          <t>14013; 32323</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26085</t>
+          <t>36189</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>33661</t>
+          <t>35702</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>59746</t>
+          <t>71890</t>
         </is>
       </c>
     </row>
@@ -2410,62 +2410,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41861; 70268</t>
+          <t>42685; 67984</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16154; 34238</t>
+          <t>16299; 34582</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22389; 43391</t>
+          <t>22463; 43239</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15264; 40003</t>
+          <t>24932; 51856</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16327; 30959</t>
+          <t>17682; 31107</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14383; 30033</t>
+          <t>15051; 30235</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28576; 47216</t>
+          <t>28556; 47952</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26026; 42273</t>
+          <t>27710; 44964</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>64510; 94477</t>
+          <t>62580; 92893</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>34134; 59226</t>
+          <t>35099; 59164</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>56083; 84598</t>
+          <t>55419; 84029</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>47396; 74000</t>
+          <t>56687; 87846</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9851</t>
+          <t>10590</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>34226</t>
+          <t>31302</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>44077</t>
+          <t>41892</t>
         </is>
       </c>
     </row>
@@ -2618,62 +2618,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6977; 20291</t>
+          <t>6460; 19958</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6289; 18192</t>
+          <t>6339; 18013</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12443; 27653</t>
+          <t>12430; 28204</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4728; 16555</t>
+          <t>5209; 17894</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7874; 20826</t>
+          <t>7670; 20513</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10459; 23143</t>
+          <t>10499; 24831</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14393; 27382</t>
+          <t>14316; 27717</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>15636; 51841</t>
+          <t>23805; 40324</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>18053; 37149</t>
+          <t>18017; 36260</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20036; 37954</t>
+          <t>20177; 38216</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29263; 50844</t>
+          <t>29548; 50100</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>23304; 60637</t>
+          <t>32980; 54534</t>
         </is>
       </c>
     </row>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>77549</t>
+          <t>97134</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>113876</t>
+          <t>115398</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>191425</t>
+          <t>212531</t>
         </is>
       </c>
     </row>
@@ -2826,62 +2826,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>123771; 166150</t>
+          <t>121184; 162733</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>69688; 100601</t>
+          <t>68592; 101076</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>78681; 112585</t>
+          <t>79689; 114016</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>62196; 97889</t>
+          <t>78078; 117943</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>76002; 104901</t>
+          <t>75100; 105759</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>72440; 103677</t>
+          <t>72880; 103075</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>74529; 104549</t>
+          <t>75610; 105648</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>82181; 133524</t>
+          <t>100512; 131590</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>204964; 256786</t>
+          <t>206311; 256365</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>152744; 193169</t>
+          <t>152324; 199139</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>162076; 208156</t>
+          <t>162334; 206760</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>156898; 217349</t>
+          <t>187823; 243152</t>
         </is>
       </c>
     </row>
